--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="215">
-  <si>
-    <t>Statement: createMemberSchema – validate input for creating a gym member. Fields: fullName (8-64 chars), email (simplified RFC 5321), dateOfBirth (YYYY-MM-DD, must be strictly past), phone (E.164: +?[1-9]\d{1,14}), password (8-64 chars, uppercase+digit+special), membershipStart (YYYY-MM-DD).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="215">
+  <si>
+    <t>Statement: createMemberSchema – Validates the input for creating a gym member using Zod safeParse. Returns { success: true, data } when all fields satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field on any violation. Required fields: email (valid email format), fullName (8–64 characters after trimming, not whitespace-only), phone (E.164 format: +[1-9]\d{1,14}), dateOfBirth (YYYY-MM-DD, strictly before today), password (8–64 characters with at least one uppercase letter, one digit, and one special character), membershipStart (YYYY-MM-DD; future dates accepted). Surrounding whitespace is trimmed from fullName, email, and phone before validation.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Input values passed to Zod.safeParse()</t>
+    <t>Input is passed directly to createMemberSchema.safeParse(). fullName rules: 8–64 characters after trim, not whitespace-only. password rules: 8–64 characters with at least one uppercase letter, one digit, and one special character. dateOfBirth: YYYY-MM-DD, strictly before today (yesterday is valid, today is not). membershipStart: YYYY-MM-DD, any date including future.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: boolean, data?, error? }</t>
+    <t>Output: { success: boolean, data?: CreateMemberInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match schema constraints</t>
+    <t>On success: parsed data matches the (trimmed) input. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,115 +64,121 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>All fields valid</t>
-  </si>
-  <si>
-    <t>All fields correct</t>
-  </si>
-  <si>
-    <t>Email presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>FullName presence</t>
-  </si>
-  <si>
-    <t>Phone presence</t>
-  </si>
-  <si>
-    <t>DateOfBirth presence</t>
-  </si>
-  <si>
-    <t>Password presence</t>
-  </si>
-  <si>
-    <t>MembershipStart presence</t>
-  </si>
-  <si>
-    <t>Email format</t>
-  </si>
-  <si>
-    <t>Valid RFC</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>Password uppercase</t>
-  </si>
-  <si>
-    <t>Has uppercase</t>
-  </si>
-  <si>
-    <t>Missing uppercase</t>
-  </si>
-  <si>
-    <t>Password number</t>
-  </si>
-  <si>
-    <t>Has number</t>
-  </si>
-  <si>
-    <t>Missing number</t>
-  </si>
-  <si>
-    <t>Password special char</t>
-  </si>
-  <si>
-    <t>Has special char</t>
-  </si>
-  <si>
-    <t>Missing special char</t>
-  </si>
-  <si>
-    <t>Phone format</t>
-  </si>
-  <si>
-    <t>Valid E.164</t>
-  </si>
-  <si>
-    <t>DateOfBirth format</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>DateOfBirth value</t>
-  </si>
-  <si>
-    <t>Past date</t>
-  </si>
-  <si>
-    <t>Future date</t>
-  </si>
-  <si>
-    <t>MembershipStart format</t>
-  </si>
-  <si>
-    <t>MembershipStart value</t>
-  </si>
-  <si>
-    <t>Any valid date (inc future)</t>
-  </si>
-  <si>
-    <t>FullName whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace (trimmed)</t>
-  </si>
-  <si>
-    <t>Whitespace-only</t>
-  </si>
-  <si>
-    <t>Email whitespace</t>
-  </si>
-  <si>
-    <t>Phone whitespace</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All fields valid → success: true, parsed data equals input</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email omitted → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>fullName presence</t>
+  </si>
+  <si>
+    <t>fullName omitted → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>phone presence</t>
+  </si>
+  <si>
+    <t>phone omitted → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>dateOfBirth presence</t>
+  </si>
+  <si>
+    <t>dateOfBirth omitted → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>password presence</t>
+  </si>
+  <si>
+    <t>password omitted → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>membershipStart presence</t>
+  </si>
+  <si>
+    <t>membershipStart omitted → success: false, error path contains "membershipStart"</t>
+  </si>
+  <si>
+    <t>email format</t>
+  </si>
+  <si>
+    <t>email: "invalidemail.com" (missing @) → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>password uppercase</t>
+  </si>
+  <si>
+    <t>password: "secure1@pass" (no uppercase letter) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password digit</t>
+  </si>
+  <si>
+    <t>password: "SecureP@ss" (no digit) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password special char</t>
+  </si>
+  <si>
+    <t>password: "SecurePass1" (no special character) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>phone format</t>
+  </si>
+  <si>
+    <t>phone: "0712345678" (no country code prefix) → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>dateOfBirth format</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "15-01-1990" (DD-MM-YYYY, wrong format) → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>dateOfBirth value</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "2099-01-01" (future date) → success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>membershipStart format</t>
+  </si>
+  <si>
+    <t>membershipStart: "01/01/2024" (MM/DD/YYYY, wrong format) → success: false, error path contains "membershipStart"</t>
+  </si>
+  <si>
+    <t>membershipStart value</t>
+  </si>
+  <si>
+    <t>membershipStart: "2099-01-01" (future date accepted) → success: true, parsed membershipStart is "2099-01-01"</t>
+  </si>
+  <si>
+    <t>fullName content</t>
+  </si>
+  <si>
+    <t>fullName: "  John Doe Test  " (surrounding whitespace) → success: true, parsed fullName is "John Doe Test"</t>
+  </si>
+  <si>
+    <t>fullName: "         " (whitespace-only) → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>email whitespace</t>
+  </si>
+  <si>
+    <t>email: "  john.doe@example.com  " (surrounding whitespace) → success: true, parsed email is "john.doe@example.com"</t>
+  </si>
+  <si>
+    <t>phone whitespace</t>
+  </si>
+  <si>
+    <t>phone: "  +40712345678  " (surrounding whitespace) → success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -193,10 +199,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid member data</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values</t>
+  </si>
+  <si>
+    <t>success: true, parsed data equals input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -205,115 +211,142 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Missing email</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>valid member data with email field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "email"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Missing fullName</t>
+    <t>valid member data with fullName field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "fullName"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing phone</t>
+    <t>valid member data with phone field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "phone"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Missing dateOfBirth</t>
+    <t>valid member data with dateOfBirth field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "dateOfBirth"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Missing password</t>
+    <t>valid member data with password field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "password"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>Missing membershipStart</t>
+    <t>valid member data with membershipStart field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "membershipStart"</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>Email="invalidemail.com"</t>
+    <t>valid member data with email: "invalidemail.com" (missing @)</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>Password="secure1@pass"</t>
+    <t>valid member data with password: "secure1@pass" (no uppercase letter)</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>Password="SecureP@ss"</t>
+    <t>valid member data with password: "SecureP@ss" (no digit)</t>
   </si>
   <si>
     <t>EC-11</t>
   </si>
   <si>
-    <t>Password="SecurePass1"</t>
+    <t>valid member data with password: "SecurePass1" (no special character)</t>
   </si>
   <si>
     <t>EC-12</t>
   </si>
   <si>
-    <t>Phone="0712345678"</t>
+    <t>valid member data with phone: "0712345678" (no country code prefix)</t>
   </si>
   <si>
     <t>EC-13</t>
   </si>
   <si>
-    <t>DateOfBirth="15-01-1990"</t>
+    <t>valid member data with dateOfBirth: "15-01-1990" (DD-MM-YYYY, wrong format)</t>
   </si>
   <si>
     <t>EC-14</t>
   </si>
   <si>
-    <t>DateOfBirth="2099-01-01"</t>
+    <t>valid member data with dateOfBirth: "2099-01-01" (future date)</t>
   </si>
   <si>
     <t>EC-15</t>
   </si>
   <si>
-    <t>MembershipStart="01/01/2024"</t>
+    <t>valid member data with membershipStart: "01/01/2024" (MM/DD/YYYY, wrong format)</t>
   </si>
   <si>
     <t>EC-16</t>
   </si>
   <si>
-    <t>MembershipStart="2099-01-01"</t>
+    <t>valid member data with membershipStart: "2099-01-01" (future date)</t>
+  </si>
+  <si>
+    <t>success: true, parsed membershipStart is "2099-01-01"</t>
   </si>
   <si>
     <t>EC-17</t>
   </si>
   <si>
-    <t>fullName="         " (whitespace only)</t>
-  </si>
-  <si>
-    <t>fullName="  John Doe Test  " (padded)</t>
+    <t>valid member data with fullName: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "  John Doe Test  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "John Doe Test"</t>
   </si>
   <si>
     <t>EC-18</t>
   </si>
   <si>
-    <t>email="  john.doe@example.com  " (padded)</t>
+    <t>valid member data with email: "  john.doe@example.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed email is "john.doe@example.com"</t>
   </si>
   <si>
     <t>EC-19</t>
   </si>
   <si>
-    <t>phone="  +40712345678  " (padded)</t>
+    <t>valid member data with phone: "  +40712345678  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -322,169 +355,208 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>FullName length</t>
-  </si>
-  <si>
-    <t>7 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>8 chars (At Min)</t>
-  </si>
-  <si>
-    <t>9 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>63 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>64 chars (At Max)</t>
-  </si>
-  <si>
-    <t>65 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>Password length</t>
-  </si>
-  <si>
-    <t>DateOfBirth boundary</t>
-  </si>
-  <si>
-    <t>Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>Today (Invalid)</t>
-  </si>
-  <si>
-    <t>Tomorrow (Invalid)</t>
-  </si>
-  <si>
-    <t>8 whitespace chars (Whitespace At Min)</t>
-  </si>
-  <si>
-    <t>8 chars padded with whitespace (At Min after trim)</t>
-  </si>
-  <si>
-    <t>64 chars padded with whitespace (At Max after trim)</t>
-  </si>
-  <si>
-    <t>65 chars padded with whitespace (Above Max after trim)</t>
+    <t>fullName length</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(7) (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(8) (min): at minimum → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(9) (min + 1): above minimum → success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(63) (max - 1): below maximum → success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(64) (max): at maximum → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(65) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(4) (length 7, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(5) (length 8, min): at minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(6) (length 9, min + 1): above minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(60) (length 63, max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(61) (length 64, max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(62) (length 65, max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth boundary</t>
+  </si>
+  <si>
+    <t>dateOfBirth: yesterday (one day before today, YYYY-MM-DD): strictly before today → success: true</t>
+  </si>
+  <si>
+    <t>dateOfBirth: today (YYYY-MM-DD): not before today → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth: tomorrow (one day after today, YYYY-MM-DD): future → success: false</t>
+  </si>
+  <si>
+    <t>fullName whitespace + trim</t>
+  </si>
+  <si>
+    <t>fullName: " ".repeat(8) (8 whitespace chars, empty after trim): invalid → success: false</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(8) + " " (8 real chars after trim, at minimum): → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(64) + " " (64 real chars after trim, at maximum): → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(65) + " " (65 real chars after trim, above maximum): → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 FullName 7ch</t>
-  </si>
-  <si>
-    <t>fullName len 7</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 8ch</t>
-  </si>
-  <si>
-    <t>fullName len 8</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 9ch</t>
-  </si>
-  <si>
-    <t>fullName len 9</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 63ch</t>
-  </si>
-  <si>
-    <t>fullName len 63</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 64ch</t>
-  </si>
-  <si>
-    <t>fullName len 64</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 65ch</t>
-  </si>
-  <si>
-    <t>fullName len 65</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 7ch</t>
-  </si>
-  <si>
-    <t>password len 7</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 8ch</t>
-  </si>
-  <si>
-    <t>password len 8</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 9ch</t>
-  </si>
-  <si>
-    <t>password len 9</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 63ch</t>
-  </si>
-  <si>
-    <t>password len 63</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 64ch</t>
-  </si>
-  <si>
-    <t>password len 64</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 65ch</t>
-  </si>
-  <si>
-    <t>password len 65</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Yesterday</t>
-  </si>
-  <si>
-    <t>dob Yesterday</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Today</t>
-  </si>
-  <si>
-    <t>dob Today</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Tomorrow</t>
-  </si>
-  <si>
-    <t>dob Tomorrow</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName=" ".repeat(8)</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 8ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(8)+" "</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 64ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(64)+" "</t>
-  </si>
-  <si>
-    <t>BVA-4 FullName padded 65ch after trim</t>
-  </si>
-  <si>
-    <t>fullName=" "+"A".repeat(65)+" "</t>
+    <t>BVA-1  (fullName=7)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(7) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (fullName=8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(8) (8 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>BVA-3  (fullName=9)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(9) (9 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-4  (fullName=63)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(63) (63 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-5  (fullName=64)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(64) (64 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-6  (fullName=65)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: "A".repeat(65) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-7  (pwd=7)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(4) (7 characters, meets all rules except minimum length)</t>
+  </si>
+  <si>
+    <t>BVA-8  (pwd=8)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(5) (8 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>BVA-9  (pwd=9)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(6) (9 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-10 (pwd=63)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(60) (63 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-11 (pwd=64)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(61) (64 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-12 (pwd=65)</t>
+  </si>
+  <si>
+    <t>valid member data with password: "P1@" + "a".repeat(62) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-13 (dob=yest)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to yesterday (one day before today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>success: true, parsed dateOfBirth is yesterday's date string</t>
+  </si>
+  <si>
+    <t>BVA-14 (dob=today)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to today (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-15 (dob=tmrw)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to tomorrow (one day after today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-16 (ws=8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: " ".repeat(8) (8 whitespace characters, empty after trim)</t>
+  </si>
+  <si>
+    <t>BVA-17 (pad→8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: " " + "A".repeat(8) + " " (8 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-18 (pad→64)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: " " + "A".repeat(64) + " " (64 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-19 (pad→65)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName: " " + "A".repeat(65) + " " (65 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -493,133 +565,61 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid member data (All fields)</t>
-  </si>
-  <si>
-    <t>Missing email field</t>
-  </si>
-  <si>
-    <t>Missing fullName field</t>
-  </si>
-  <si>
-    <t>Missing phone field</t>
-  </si>
-  <si>
-    <t>Missing dateOfBirth field</t>
-  </si>
-  <si>
-    <t>Missing password field</t>
-  </si>
-  <si>
-    <t>Missing membershipStart field</t>
-  </si>
-  <si>
-    <t>Email="invalidemail.com" (Wrong format)</t>
-  </si>
-  <si>
-    <t>Password="secure1@pass" (No uppercase)</t>
-  </si>
-  <si>
-    <t>Password="SecureP@ss" (No number)</t>
-  </si>
-  <si>
-    <t>Password="SecurePass1" (No special)</t>
-  </si>
-  <si>
-    <t>Phone="0712345678" (No + prefix)</t>
-  </si>
-  <si>
-    <t>DateOfBirth="15-01-1990" (Wrong separator)</t>
-  </si>
-  <si>
-    <t>DateOfBirth="2099-01-01" (Future date)</t>
-  </si>
-  <si>
-    <t>MembershipStart="01/01/2024" (Wrong separator)</t>
-  </si>
-  <si>
-    <t>MembershipStart="2099-01-01" (Future membership)</t>
-  </si>
-  <si>
-    <t>FullName whitespace-only</t>
-  </si>
-  <si>
-    <t>FullName with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Email with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Phone with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>fullName len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>fullName len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>fullName len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>fullName len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>fullName len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>password len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>password len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>password len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>password len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>password len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>password len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>dob Yesterday (Boundary valid)</t>
-  </si>
-  <si>
-    <t>dob Today (Boundary invalid)</t>
-  </si>
-  <si>
-    <t>dob Tomorrow (Boundary invalid)</t>
-  </si>
-  <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>fullName whitespace 8ch</t>
-  </si>
-  <si>
-    <t>fullName padded → 8ch after trim (At Min)</t>
-  </si>
-  <si>
-    <t>fullName padded → 64ch after trim (At Max)</t>
-  </si>
-  <si>
-    <t>fullName padded → 65ch after trim (Above Max)</t>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
   </si>
   <si>
     <t>Testing</t>
@@ -652,7 +652,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-01</t>
+    <t>SCHEMA-01</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1221,10 +1221,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1232,13 +1232,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1249,10 +1249,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1260,13 +1260,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1274,13 +1274,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1288,13 +1288,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,13 +1302,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1316,13 +1316,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1330,13 +1330,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1344,10 +1344,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>36</v>
@@ -1361,10 +1361,10 @@
         <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,10 +1375,10 @@
         <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,10 +1389,10 @@
         <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,13 +1400,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,7 +1445,7 @@
         <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>1</v>
@@ -1456,10 +1456,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1</v>
@@ -1485,19 +1485,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1505,16 +1505,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1522,16 +1522,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1539,16 +1539,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1556,16 +1556,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1573,16 +1573,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1590,16 +1590,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1607,16 +1607,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1624,16 +1624,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1641,16 +1641,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1658,16 +1658,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1675,16 +1675,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1692,16 +1692,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1709,16 +1709,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1726,16 +1726,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1743,16 +1743,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1760,16 +1760,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1777,16 +1777,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1794,16 +1794,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1811,16 +1811,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1828,16 +1828,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1858,13 +1858,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1872,208 +1872,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
+      <c r="A19" s="1">
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>1</v>
+      <c r="A20" s="1">
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2096,19 +2096,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2116,16 +2116,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2133,16 +2133,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2150,16 +2150,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2167,16 +2167,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2184,16 +2184,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2201,16 +2201,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2218,16 +2218,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2235,16 +2235,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,16 +2252,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2269,16 +2269,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2286,16 +2286,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2303,16 +2303,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2320,16 +2320,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2337,16 +2337,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2354,16 +2354,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2371,16 +2371,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2388,16 +2388,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,16 +2405,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2422,16 +2422,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2455,22 +2455,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2478,19 +2478,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2498,19 +2498,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2518,19 +2518,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2538,19 +2538,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,19 +2558,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,19 +2578,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2598,19 +2598,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2618,19 +2618,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2638,19 +2638,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2658,19 +2658,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2678,19 +2678,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2698,19 +2698,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,19 +2718,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2738,19 +2738,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2758,19 +2758,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2778,19 +2778,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2798,19 +2798,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,19 +2818,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,19 +2838,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,19 +2858,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2901,16 +2901,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2921,16 +2921,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2941,16 +2941,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,16 +2961,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,16 +2981,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,16 +3001,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,16 +3021,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3041,16 +3041,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3061,16 +3061,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,16 +3081,16 @@
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3101,16 +3101,16 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3121,16 +3121,16 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3141,16 +3141,16 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3161,16 +3161,16 @@
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3181,16 +3181,16 @@
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3201,16 +3201,16 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,16 +3221,16 @@
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,16 +3241,16 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/createMemberSchema-bbt-form.xlsx
@@ -652,7 +652,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-01</t>
+    <t>SCHEMA-02</t>
   </si>
   <si>
     <t>n/a</t>
